--- a/Result/profitability/2070.xlsx
+++ b/Result/profitability/2070.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM44"/>
+  <dimension ref="A1:AM45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6022,6 +6022,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>190</v>
+      </c>
+      <c r="D45" t="n">
+        <v>89</v>
+      </c>
+      <c r="E45" t="n">
+        <v>101</v>
+      </c>
+      <c r="F45" t="n">
+        <v>53.07</v>
+      </c>
+      <c r="G45" t="n">
+        <v>38</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>20.24%</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>6</v>
+      </c>
+      <c r="J45" t="n">
+        <v>44</v>
+      </c>
+      <c r="K45" t="n">
+        <v>40</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.60625</v>
+      </c>
+      <c r="N45" t="n">
+        <v>48.44</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
+      </c>
+      <c r="V45" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0.6799999999999999</v>
+      </c>
+      <c r="X45" t="n">
+        <v>2.428571428571428</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>6.439999999999998</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0.1381085138322968</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0.8899999999999999</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>12.71428571428571</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.133489961554891</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK45" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
